--- a/指令.xlsx
+++ b/指令.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>单位：Bit</t>
   </si>
@@ -37,7 +37,7 @@
     <t>2(数据高位)</t>
   </si>
   <si>
-    <t>8(数据低位)</t>
+    <t>9(数据低位)</t>
   </si>
   <si>
     <t>帧头</t>
@@ -49,9 +49,6 @@
     <t>数据</t>
   </si>
   <si>
-    <t>XOR校验(由程序添加)</t>
-  </si>
-  <si>
     <t>0xA5</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
   </si>
   <si>
     <t>0x01</t>
-  </si>
-  <si>
-    <t>/</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1080,7 @@
     <col min="9" max="9" width="9.8018018018018" customWidth="1"/>
     <col min="10" max="10" width="9.42342342342342" customWidth="1"/>
     <col min="11" max="11" width="12.3513513513514" customWidth="1"/>
-    <col min="12" max="12" width="21.2252252252252" customWidth="1"/>
+    <col min="12" max="12" width="12.1261261261261" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="14.85" spans="2:12">
@@ -1117,14 +1111,14 @@
       <c r="J2" s="1">
         <v>7</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="1">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="14.85" spans="3:12">
+    </row>
+    <row r="3" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1139,20 +1133,18 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="2" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="3:12">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" ht="14.85" spans="3:12">
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -1160,13 +1152,11 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="14.85" spans="3:12">
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="3:12">
       <c r="C5" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -1176,13 +1166,11 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="14.85" spans="3:12">
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="3:12">
       <c r="C6" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -1192,13 +1180,11 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" ht="14.85" spans="3:12">
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="3:12">
       <c r="C7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -1208,13 +1194,11 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
-      <c r="L7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" ht="14.85" spans="3:12">
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="3:12">
       <c r="C8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -1224,13 +1208,11 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" ht="14.85" spans="3:12">
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="3:12">
       <c r="C9" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -1240,11 +1222,9 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" ht="14.85" spans="3:12">
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="3:12">
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -1254,11 +1234,9 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="L10" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" ht="14.85" spans="3:12">
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="3:12">
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -1268,11 +1246,9 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
-      <c r="L11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="14.85" spans="3:12">
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="3:12">
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -1282,11 +1258,9 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
-      <c r="L12" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" ht="14.85" spans="3:12">
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="3:12">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1296,11 +1270,9 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
-      <c r="L13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" ht="14.85" spans="3:12">
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="3:12">
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -1310,11 +1282,9 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
-      <c r="L14" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" ht="14.85" spans="3:12">
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="3:12">
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -1324,11 +1294,9 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
-      <c r="L15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" ht="14.85" spans="3:12">
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="3:12">
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -1338,11 +1306,9 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
-      <c r="L16" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" ht="14.85" spans="3:12">
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="3:12">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -1352,11 +1318,9 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
-      <c r="L17" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" ht="14.85" spans="3:12">
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="3:12">
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -1366,11 +1330,9 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
-      <c r="L18" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" ht="14.85" spans="3:12">
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="3:12">
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -1380,13 +1342,11 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
-      <c r="L19" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="L19" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E3:K3"/>
+    <mergeCell ref="E3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
